--- a/report-001-manual-001.xlsx
+++ b/report-001-manual-001.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>{"baseline_commit": "2f2d103444a865bace68feaf166b8c5ce1c6c653", "fix_commit": "0275786b2413e726a00cfdb3c12d8245f2079c8e", "fix_passed": true, "red_failed": true, "test_commit": "d11cf73e24f661e073c871ad74a6aa8625b5669a"}</t>
+          <t>{"post_fix": {"commit": "0275786b2413e726a00cfdb3c12d8245f2079c8e", "result": "green", "trajectory_url": "未生成"}, "pre_fix": {"commit": "d11cf73e24f661e073c871ad74a6aa8625b5669a", "result": "red", "trajectory_url": "未生成"}}</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
